--- a/engineering_basics/pf/pf.xlsx
+++ b/engineering_basics/pf/pf.xlsx
@@ -5,13 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Partial Fraction Instructions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Partial Fraction Instructions_2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Partial Fraction Instructions-1" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Program Definitions" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Partial Fraction Instructions" sheetId="1" state="hidden" r:id="rId3"/>
+    <sheet name="Partial Fraction Instructions_2" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="Partial Fraction Instructions-F" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -57,7 +56,6 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Based on the fast identity matrix creation code in https://www.hpmuseum.org/cgi-sys/cgiwrap/hpmuseum/archv016.cgi?read=91641</t>
         </r>
@@ -73,6 +71,18 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://www.symbolab.com/solver/partial-fractions-calculator/partial%20fractions%20%5Cfrac%7B%5Cleft(2x-1%5Cright)%7D%7B%5Cleft(x-2%5Cright)%5Cleft(x-2%5Cright)%5Cleft(x-2%5Cright)%5Cleft(x-3%5Cright)%5Cleft(x-3%5Cright)%7D?or=input</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0">
       <text>
         <r>
@@ -80,7 +90,6 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Based on the fast identity matrix creation code in https://www.hpmuseum.org/cgi-sys/cgiwrap/hpmuseum/archv016.cgi?read=91641</t>
         </r>
@@ -91,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="229">
   <si>
     <t xml:space="preserve">Line Num</t>
   </si>
@@ -864,6 +873,39 @@
     <t xml:space="preserve">LBL 7</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Load x-x</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> of the binomial to be convolved (root stored in R.5)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Program: requires matrix A defined as a 2xN matrix</t>
+  </si>
+  <si>
     <t xml:space="preserve">44 16 15</t>
   </si>
   <si>
@@ -882,11 +924,12 @@
     <numFmt numFmtId="165" formatCode="000"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1001,12 +1044,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF333333"/>
@@ -1051,11 +1088,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFC9211E"/>
@@ -1089,12 +1121,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1552,80 +1578,80 @@
     <xf numFmtId="164" fontId="16" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="7" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="15" borderId="8" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="15" borderId="8" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="9" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="18" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="18" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="26" fillId="20" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1633,63 +1659,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="21" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="21" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="22" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="22" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="23" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="23" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="24" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="24" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="25" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="25" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="26" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="26" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="27" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="27" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="27" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="27" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4355,10 +4377,10 @@
       <c r="C116" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D116" s="0"/>
-      <c r="E116" s="0"/>
-      <c r="F116" s="0"/>
-      <c r="G116" s="0"/>
+      <c r="D116" s="15"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="15"/>
+      <c r="G116" s="15"/>
       <c r="H116" s="16"/>
     </row>
     <row r="117" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4371,10 +4393,10 @@
       <c r="C117" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="D117" s="0"/>
-      <c r="E117" s="0"/>
-      <c r="F117" s="0"/>
-      <c r="G117" s="0"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="15"/>
+      <c r="G117" s="15"/>
       <c r="H117" s="16"/>
     </row>
     <row r="118" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4387,10 +4409,10 @@
       <c r="C118" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D118" s="0"/>
-      <c r="E118" s="0"/>
-      <c r="F118" s="0"/>
-      <c r="G118" s="0"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="15"/>
+      <c r="F118" s="15"/>
+      <c r="G118" s="15"/>
       <c r="H118" s="16"/>
     </row>
     <row r="119" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4403,10 +4425,10 @@
       <c r="C119" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="0"/>
-      <c r="E119" s="0"/>
-      <c r="F119" s="0"/>
-      <c r="G119" s="0"/>
+      <c r="D119" s="15"/>
+      <c r="E119" s="15"/>
+      <c r="F119" s="15"/>
+      <c r="G119" s="15"/>
       <c r="H119" s="16"/>
     </row>
     <row r="120" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7355,10 +7377,10 @@
       <c r="C116" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D116" s="0"/>
-      <c r="E116" s="0"/>
-      <c r="F116" s="0"/>
-      <c r="G116" s="0"/>
+      <c r="D116" s="15"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="15"/>
+      <c r="G116" s="15"/>
       <c r="H116" s="16"/>
     </row>
     <row r="117" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7371,10 +7393,10 @@
       <c r="C117" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D117" s="0"/>
-      <c r="E117" s="0"/>
-      <c r="F117" s="0"/>
-      <c r="G117" s="0"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="15"/>
+      <c r="G117" s="15"/>
       <c r="H117" s="16"/>
     </row>
     <row r="118" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7387,10 +7409,10 @@
       <c r="C118" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D118" s="0"/>
-      <c r="E118" s="0"/>
-      <c r="F118" s="0"/>
-      <c r="G118" s="0"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="15"/>
+      <c r="F118" s="15"/>
+      <c r="G118" s="15"/>
       <c r="H118" s="16"/>
     </row>
     <row r="119" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7403,10 +7425,10 @@
       <c r="C119" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D119" s="0"/>
-      <c r="E119" s="0"/>
-      <c r="F119" s="0"/>
-      <c r="G119" s="0"/>
+      <c r="D119" s="15"/>
+      <c r="E119" s="15"/>
+      <c r="F119" s="15"/>
+      <c r="G119" s="15"/>
       <c r="H119" s="16"/>
     </row>
     <row r="120" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7419,10 +7441,10 @@
       <c r="C120" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D120" s="0"/>
-      <c r="E120" s="0"/>
-      <c r="F120" s="0"/>
-      <c r="G120" s="0"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="15"/>
+      <c r="G120" s="15"/>
       <c r="H120" s="16"/>
     </row>
     <row r="121" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7838,40 +7860,40 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C145" s="0"/>
+      <c r="C145" s="15"/>
     </row>
     <row r="146" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C146" s="0"/>
+      <c r="C146" s="15"/>
     </row>
     <row r="147" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C147" s="0"/>
+      <c r="C147" s="15"/>
     </row>
     <row r="148" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C148" s="0"/>
+      <c r="C148" s="15"/>
     </row>
     <row r="149" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C149" s="0"/>
+      <c r="C149" s="15"/>
     </row>
     <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C150" s="0"/>
+      <c r="C150" s="15"/>
     </row>
     <row r="151" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C151" s="0"/>
+      <c r="C151" s="15"/>
     </row>
     <row r="152" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C152" s="0"/>
+      <c r="C152" s="15"/>
     </row>
     <row r="153" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C153" s="0"/>
+      <c r="C153" s="15"/>
     </row>
     <row r="154" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C154" s="0"/>
+      <c r="C154" s="15"/>
     </row>
     <row r="155" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C155" s="0"/>
+      <c r="C155" s="15"/>
     </row>
     <row r="156" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C156" s="0"/>
+      <c r="C156" s="15"/>
     </row>
     <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -8184,7 +8206,7 @@
       </c>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="n">
         <v>9</v>
       </c>
@@ -8194,32 +8216,22 @@
       <c r="C11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>38</v>
-      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="10"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>39</v>
+      <c r="B12" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>37</v>
@@ -8234,7 +8246,7 @@
         <v>12</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>41</v>
+        <v>224</v>
       </c>
       <c r="M12" s="1"/>
     </row>
@@ -8242,18 +8254,18 @@
       <c r="A13" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>34</v>
+      <c r="B13" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="E13" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="F13" s="9" t="s">
         <v>12</v>
       </c>
@@ -8261,7 +8273,7 @@
         <v>12</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M13" s="1"/>
     </row>
@@ -8269,11 +8281,11 @@
       <c r="A14" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>44</v>
+      <c r="B14" s="9" t="n">
+        <v>34</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>1</v>
@@ -8288,7 +8300,7 @@
         <v>12</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M14" s="1"/>
     </row>
@@ -8297,10 +8309,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>1</v>
@@ -8315,7 +8327,7 @@
         <v>12</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M15" s="1"/>
     </row>
@@ -8324,10 +8336,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>49</v>
+        <v>29</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>1</v>
@@ -8342,68 +8354,71 @@
         <v>12</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>50</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="M16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="12" t="s">
+      <c r="D18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F18" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="13" t="s">
+      <c r="G18" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>193</v>
+        <v>54</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>12</v>
@@ -8417,17 +8432,19 @@
       <c r="G19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="10"/>
+      <c r="H19" s="10" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>12</v>
@@ -8448,16 +8465,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>15</v>
+        <v>211</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>12</v>
@@ -8465,46 +8482,43 @@
       <c r="G21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>18</v>
-      </c>
+      <c r="H21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>36</v>
+      <c r="B22" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>12</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="M22" s="1"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>58</v>
+      <c r="B23" s="9" t="n">
+        <v>36</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>16</v>
@@ -8519,7 +8533,7 @@
         <v>12</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M23" s="1"/>
     </row>
@@ -8528,10 +8542,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>16</v>
@@ -8542,9 +8556,11 @@
       <c r="F24" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="9"/>
+      <c r="G24" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="H24" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M24" s="1"/>
     </row>
@@ -8552,36 +8568,36 @@
       <c r="A25" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>0</v>
+      <c r="B25" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="10"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="M25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>225</v>
+      <c r="B26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>0</v>
@@ -8602,20 +8618,20 @@
       <c r="A27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="9" t="n">
-        <v>33</v>
+      <c r="B27" s="9" t="s">
+        <v>226</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>16</v>
+        <v>227</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>17</v>
@@ -8628,19 +8644,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>17</v>
@@ -8652,11 +8668,11 @@
       <c r="A29" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>95</v>
+      <c r="B29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>1</v>
@@ -8677,17 +8693,17 @@
       <c r="A30" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="9" t="n">
-        <v>34</v>
+      <c r="B30" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>1</v>
+        <v>95</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>16</v>
@@ -8695,19 +8711,18 @@
       <c r="G30" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>64</v>
-      </c>
+      <c r="H30" s="10"/>
+      <c r="M30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>65</v>
+      <c r="B31" s="9" t="n">
+        <v>34</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>16</v>
@@ -8721,17 +8736,19 @@
       <c r="G31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="10"/>
+      <c r="H31" s="10" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="9" t="n">
-        <v>26</v>
+      <c r="B32" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>16</v>
@@ -8752,10 +8769,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>3</v>
+        <v>26</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>16</v>
@@ -8769,19 +8786,17 @@
       <c r="G33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>68</v>
-      </c>
+      <c r="H33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="n">
         <v>32</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>69</v>
+        <v>3</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>16</v>
@@ -8795,20 +8810,22 @@
       <c r="G34" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H34" s="10"/>
+      <c r="H34" s="10" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="n">
         <v>33</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="E35" s="9" t="n">
         <v>1</v>
@@ -8819,43 +8836,43 @@
       <c r="G35" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="10" t="s">
-        <v>68</v>
-      </c>
+      <c r="H35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="n">
         <v>34</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>16</v>
+        <v>71</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="10"/>
+      <c r="H36" s="10" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>74</v>
+      <c r="B37" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>73</v>
@@ -8876,10 +8893,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>73</v>
@@ -8893,19 +8910,17 @@
       <c r="G38" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H38" s="10" t="s">
-        <v>78</v>
-      </c>
+      <c r="H38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="n">
         <v>37</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>73</v>
@@ -8920,7 +8935,7 @@
         <v>17</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8928,10 +8943,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>73</v>
@@ -8945,17 +8960,19 @@
       <c r="G40" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H40" s="10"/>
+      <c r="H40" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="n">
         <v>39</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>93</v>
+        <v>82</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>73</v>
@@ -8969,19 +8986,17 @@
       <c r="G41" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H41" s="9" t="s">
-        <v>17</v>
-      </c>
+      <c r="H41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>73</v>
@@ -8995,45 +9010,45 @@
       <c r="G42" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="10" t="s">
-        <v>86</v>
+      <c r="H42" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>0</v>
+      <c r="B43" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>85</v>
+      <c r="B44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D44" s="9" t="n">
         <v>0</v>
@@ -9048,71 +9063,71 @@
         <v>17</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>1</v>
+      <c r="B45" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="E45" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="F45" s="9" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="10"/>
+        <v>17</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>98</v>
+      <c r="B46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="F46" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="G46" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>16</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E47" s="9" t="n">
         <v>1</v>
@@ -9132,10 +9147,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>101</v>
@@ -9149,22 +9164,32 @@
       <c r="G48" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="H48" s="10"/>
+      <c r="H48" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="n">
         <v>47</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
+        <v>106</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="H49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9172,10 +9197,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>125</v>
+        <v>108</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>109</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
@@ -9188,10 +9213,10 @@
         <v>49</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>111</v>
+        <v>124</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
@@ -9203,70 +9228,68 @@
       <c r="A52" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>2</v>
+      <c r="B52" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
-      <c r="H52" s="10" t="s">
-        <v>112</v>
-      </c>
+      <c r="H52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>114</v>
+      <c r="B53" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
-      <c r="H53" s="10"/>
+      <c r="H53" s="10" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="n">
         <v>52</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
-      <c r="H54" s="10" t="s">
-        <v>86</v>
-      </c>
+      <c r="H54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="n">
         <v>53</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="10" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9274,17 +9297,17 @@
         <v>54</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9292,17 +9315,17 @@
         <v>55</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
       <c r="H57" s="10" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9310,28 +9333,28 @@
         <v>56</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="10" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="9" t="n">
-        <v>30</v>
+      <c r="B59" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
@@ -9345,18 +9368,18 @@
       <c r="A60" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="9" t="s">
-        <v>121</v>
+      <c r="B60" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="10" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9364,17 +9387,17 @@
         <v>59</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="10" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9382,26 +9405,28 @@
         <v>60</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>213</v>
+        <v>119</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
-      <c r="H62" s="10"/>
+      <c r="H62" s="10" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="n">
         <v>61</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>215</v>
+        <v>212</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -9414,35 +9439,33 @@
         <v>62</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>127</v>
+        <v>214</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>215</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
-      <c r="H64" s="10" t="s">
-        <v>128</v>
-      </c>
+      <c r="H64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="n">
         <v>63</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
       <c r="H65" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9450,17 +9473,17 @@
         <v>64</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="10" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9468,10 +9491,10 @@
         <v>65</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
@@ -9485,11 +9508,11 @@
       <c r="A68" s="9" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="9" t="n">
-        <v>20</v>
+      <c r="B68" s="9" t="s">
+        <v>134</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
@@ -9503,18 +9526,18 @@
       <c r="A69" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="9" t="s">
-        <v>136</v>
+      <c r="B69" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
       <c r="G69" s="9"/>
       <c r="H69" s="10" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9522,17 +9545,17 @@
         <v>68</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="10" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9540,17 +9563,17 @@
         <v>69</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
       <c r="H71" s="10" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9558,51 +9581,51 @@
         <v>70</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>143</v>
+        <v>139</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>140</v>
       </c>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
-      <c r="H72" s="10"/>
+      <c r="H72" s="10" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="n">
         <v>71</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>97</v>
+        <v>142</v>
+      </c>
+      <c r="C73" s="24" t="s">
+        <v>143</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
-      <c r="H73" s="10" t="s">
-        <v>144</v>
-      </c>
+      <c r="H73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="n">
         <v>72</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="10" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9610,10 +9633,10 @@
         <v>73</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
@@ -9627,11 +9650,11 @@
       <c r="A76" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" s="11" t="n">
-        <v>1</v>
+      <c r="B76" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>146</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
@@ -9645,11 +9668,11 @@
       <c r="A77" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>148</v>
+      <c r="B77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
@@ -9664,17 +9687,17 @@
         <v>76</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="10" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9682,17 +9705,17 @@
         <v>77</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>151</v>
+        <v>93</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,26 +9723,28 @@
         <v>78</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C80" s="26" t="s">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
-      <c r="H80" s="10"/>
+      <c r="H80" s="10" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" s="11" t="n">
-        <v>1</v>
+      <c r="B81" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C81" s="26" t="s">
+        <v>154</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
@@ -9731,11 +9756,11 @@
       <c r="A82" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>156</v>
+      <c r="B82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
@@ -9748,69 +9773,67 @@
         <v>81</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
-      <c r="H83" s="10" t="s">
-        <v>144</v>
-      </c>
+      <c r="H83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="n">
         <v>82</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
-      <c r="H84" s="10"/>
+      <c r="H84" s="10" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="11" t="n">
-        <v>0</v>
+      <c r="B85" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
-      <c r="H85" s="10" t="s">
-        <v>68</v>
-      </c>
+      <c r="H85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>162</v>
+      <c r="B86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
       <c r="F86" s="9"/>
       <c r="G86" s="9"/>
       <c r="H86" s="10" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9818,17 +9841,17 @@
         <v>85</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C87" s="26" t="s">
-        <v>165</v>
+        <v>161</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>162</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
       <c r="G87" s="9"/>
       <c r="H87" s="10" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9836,17 +9859,17 @@
         <v>86</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
+      </c>
+      <c r="C88" s="26" t="s">
+        <v>165</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
       <c r="H88" s="10" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9854,17 +9877,17 @@
         <v>87</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>169</v>
+        <v>166</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
       <c r="H89" s="10" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9872,17 +9895,17 @@
         <v>88</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>169</v>
       </c>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
       <c r="H90" s="10" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9890,26 +9913,28 @@
         <v>89</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
-      <c r="H91" s="10"/>
+      <c r="H91" s="10" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="n">
         <v>90</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
@@ -9922,10 +9947,10 @@
         <v>91</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -9938,10 +9963,10 @@
         <v>92</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -9953,11 +9978,11 @@
       <c r="A95" s="9" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="9" t="n">
-        <v>10</v>
+      <c r="B95" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
@@ -9969,11 +9994,11 @@
       <c r="A96" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="9" t="s">
-        <v>170</v>
+      <c r="B96" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
@@ -9986,10 +10011,10 @@
         <v>95</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
@@ -10002,10 +10027,10 @@
         <v>96</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
@@ -10018,10 +10043,10 @@
         <v>97</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
@@ -10034,10 +10059,10 @@
         <v>98</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
@@ -10050,10 +10075,10 @@
         <v>99</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>65</v>
+        <v>179</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>66</v>
+        <v>180</v>
       </c>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
@@ -10066,10 +10091,10 @@
         <v>100</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
@@ -10082,10 +10107,10 @@
         <v>101</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
@@ -10098,23 +10123,15 @@
         <v>102</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C104" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E104" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G104" s="9" t="s">
-        <v>12</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D104" s="9"/>
+      <c r="E104" s="9"/>
+      <c r="F104" s="9"/>
+      <c r="G104" s="9"/>
       <c r="H104" s="10"/>
     </row>
     <row r="105" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10122,10 +10139,10 @@
         <v>103</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>193</v>
+        <v>181</v>
+      </c>
+      <c r="C105" s="22" t="s">
+        <v>182</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>12</v>
@@ -10146,10 +10163,10 @@
         <v>104</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>12</v>
@@ -10169,14 +10186,14 @@
       <c r="A107" s="9" t="n">
         <v>105</v>
       </c>
-      <c r="B107" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C107" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D107" s="11" t="n">
-        <v>2</v>
+      <c r="B107" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>12</v>
@@ -10193,17 +10210,17 @@
       <c r="A108" s="9" t="n">
         <v>106</v>
       </c>
-      <c r="B108" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D108" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E108" s="11" t="n">
+      <c r="B108" s="9" t="n">
         <v>2</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>12</v>
@@ -10218,10 +10235,10 @@
         <v>107</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>101</v>
@@ -10235,75 +10252,75 @@
       <c r="G109" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H109" s="16"/>
+      <c r="H109" s="10"/>
     </row>
     <row r="110" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="9" t="n">
         <v>108</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E110" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F110" s="11" t="n">
+      <c r="E110" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G110" s="11"/>
+      <c r="F110" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="H110" s="16"/>
     </row>
     <row r="111" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="9" t="n">
         <v>109</v>
       </c>
-      <c r="B111" s="9" t="n">
+      <c r="B111" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E111" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F111" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C111" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D111" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G111" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="G111" s="11"/>
       <c r="H111" s="16"/>
     </row>
     <row r="112" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="9" t="n">
         <v>110</v>
       </c>
-      <c r="B112" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D112" s="11" t="s">
+      <c r="B112" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F112" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E112" s="11" t="n">
+      <c r="G112" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="F112" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="G112" s="11" t="s">
-        <v>101</v>
       </c>
       <c r="H112" s="16"/>
     </row>
@@ -10312,10 +10329,10 @@
         <v>111</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>101</v>
@@ -10335,23 +10352,23 @@
       <c r="A114" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="B114" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C114" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="11" t="s">
+      <c r="B114" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D114" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F114" s="11" t="n">
+      <c r="E114" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="F114" s="11" t="s">
+        <v>185</v>
+      </c>
       <c r="G114" s="11" t="s">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="H114" s="16"/>
     </row>
@@ -10360,19 +10377,19 @@
         <v>113</v>
       </c>
       <c r="B115" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C115" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="E115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F115" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="F115" s="11" t="s">
-        <v>185</v>
       </c>
       <c r="G115" s="11" t="s">
         <v>185</v>
@@ -10383,20 +10400,20 @@
       <c r="A116" s="9" t="n">
         <v>114</v>
       </c>
-      <c r="B116" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>116</v>
+      <c r="B116" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="E116" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="F116" s="11" t="n">
+      <c r="E116" s="11" t="n">
         <v>2</v>
+      </c>
+      <c r="F116" s="11" t="s">
+        <v>185</v>
       </c>
       <c r="G116" s="11" t="s">
         <v>185</v>
@@ -10408,22 +10425,22 @@
         <v>115</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="D117" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E117" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="E117" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F117" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="G117" s="11" t="n">
-        <v>2</v>
       </c>
       <c r="H117" s="16"/>
     </row>
@@ -10432,15 +10449,23 @@
         <v>116</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
-      <c r="G118" s="11"/>
+        <v>189</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G118" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="H118" s="16"/>
     </row>
     <row r="119" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10448,15 +10473,15 @@
         <v>117</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D119" s="0"/>
-      <c r="E119" s="0"/>
-      <c r="F119" s="0"/>
-      <c r="G119" s="0"/>
+        <v>191</v>
+      </c>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="11"/>
       <c r="H119" s="16"/>
     </row>
     <row r="120" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10464,15 +10489,15 @@
         <v>118</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D120" s="0"/>
-      <c r="E120" s="0"/>
-      <c r="F120" s="0"/>
-      <c r="G120" s="0"/>
+        <v>184</v>
+      </c>
+      <c r="D120" s="15"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="15"/>
+      <c r="G120" s="15"/>
       <c r="H120" s="16"/>
     </row>
     <row r="121" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10480,15 +10505,15 @@
         <v>119</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D121" s="0"/>
-      <c r="E121" s="0"/>
-      <c r="F121" s="0"/>
-      <c r="G121" s="0"/>
+        <v>191</v>
+      </c>
+      <c r="D121" s="15"/>
+      <c r="E121" s="15"/>
+      <c r="F121" s="15"/>
+      <c r="G121" s="15"/>
       <c r="H121" s="16"/>
     </row>
     <row r="122" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10496,15 +10521,15 @@
         <v>120</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C122" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D122" s="0"/>
-      <c r="E122" s="0"/>
-      <c r="F122" s="0"/>
-      <c r="G122" s="0"/>
+        <v>216</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D122" s="15"/>
+      <c r="E122" s="15"/>
+      <c r="F122" s="15"/>
+      <c r="G122" s="15"/>
       <c r="H122" s="16"/>
     </row>
     <row r="123" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10512,44 +10537,42 @@
         <v>121</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C123" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="D123" s="0"/>
-      <c r="E123" s="0"/>
-      <c r="F123" s="0"/>
-      <c r="G123" s="0"/>
+        <v>51</v>
+      </c>
+      <c r="C123" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D123" s="15"/>
+      <c r="E123" s="15"/>
+      <c r="F123" s="15"/>
+      <c r="G123" s="15"/>
       <c r="H123" s="16"/>
     </row>
     <row r="124" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="9" t="n">
         <v>122</v>
       </c>
-      <c r="B124" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C124" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="18"/>
-      <c r="F124" s="18"/>
-      <c r="G124" s="18"/>
+      <c r="B124" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C124" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="D124" s="15"/>
+      <c r="E124" s="15"/>
+      <c r="F124" s="15"/>
+      <c r="G124" s="15"/>
       <c r="H124" s="16"/>
     </row>
     <row r="125" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="9" t="n">
         <v>123</v>
       </c>
-      <c r="B125" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C125" s="18" t="s">
-        <v>195</v>
+      <c r="B125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="D125" s="18" t="n">
         <v>1</v>
@@ -10564,10 +10587,10 @@
         <v>124</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="D126" s="18" t="n">
         <v>1</v>
@@ -10582,12 +10605,14 @@
         <v>125</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="D127" s="18"/>
+        <v>219</v>
+      </c>
+      <c r="D127" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="E127" s="18"/>
       <c r="F127" s="18"/>
       <c r="G127" s="18"/>
@@ -10598,10 +10623,10 @@
         <v>126</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>94</v>
+        <v>220</v>
       </c>
       <c r="C128" s="18" t="s">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="D128" s="18"/>
       <c r="E128" s="18"/>
@@ -10613,18 +10638,14 @@
       <c r="A129" s="9" t="n">
         <v>127</v>
       </c>
-      <c r="B129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C129" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D129" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" s="18" t="n">
-        <v>1</v>
-      </c>
+      <c r="B129" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C129" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D129" s="18"/>
+      <c r="E129" s="18"/>
       <c r="F129" s="18"/>
       <c r="G129" s="18"/>
       <c r="H129" s="16"/>
@@ -10633,24 +10654,20 @@
       <c r="A130" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="B130" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C130" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="D130" s="18" t="s">
-        <v>198</v>
+      <c r="B130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="E130" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="F130" s="18"/>
+      <c r="G130" s="18"/>
       <c r="H130" s="16"/>
     </row>
     <row r="131" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10658,13 +10675,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="D131" s="18" t="n">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="D131" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="E131" s="18" t="n">
         <v>1</v>
@@ -10673,7 +10690,7 @@
         <v>1</v>
       </c>
       <c r="G131" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" s="16"/>
     </row>
@@ -10682,13 +10699,13 @@
         <v>130</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D132" s="18" t="s">
-        <v>101</v>
+        <v>201</v>
+      </c>
+      <c r="D132" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="E132" s="18" t="n">
         <v>1</v>
@@ -10706,10 +10723,10 @@
         <v>131</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D133" s="18" t="s">
         <v>101</v>
@@ -10730,10 +10747,10 @@
         <v>132</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>220</v>
+        <v>99</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>221</v>
+        <v>100</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>101</v>
@@ -10754,10 +10771,10 @@
         <v>133</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>103</v>
+        <v>220</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>221</v>
       </c>
       <c r="D135" s="18" t="s">
         <v>101</v>
@@ -10778,10 +10795,10 @@
         <v>134</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C136" s="18" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>101</v>
@@ -10802,10 +10819,10 @@
         <v>135</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>101</v>
@@ -10826,22 +10843,22 @@
         <v>136</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C138" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="D138" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E138" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F138" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G138" s="9" t="s">
-        <v>12</v>
+        <v>51</v>
+      </c>
+      <c r="C138" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="H138" s="16"/>
     </row>
@@ -10850,15 +10867,23 @@
         <v>137</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C139" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="D139" s="18"/>
-      <c r="E139" s="18"/>
-      <c r="F139" s="18"/>
-      <c r="G139" s="18"/>
+        <v>222</v>
+      </c>
+      <c r="C139" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="H139" s="16"/>
     </row>
     <row r="140" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10866,11 +10891,15 @@
         <v>138</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>113</v>
+        <v>204</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>114</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="18"/>
+      <c r="G140" s="18"/>
       <c r="H140" s="16"/>
     </row>
     <row r="141" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10878,22 +10907,22 @@
         <v>139</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="H141" s="10"/>
+        <v>114</v>
+      </c>
+      <c r="H141" s="16"/>
     </row>
     <row r="142" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="9" t="n">
         <v>140</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>51</v>
+        <v>206</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="H142" s="10"/>
     </row>
@@ -10902,10 +10931,10 @@
         <v>141</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>208</v>
+        <v>51</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>209</v>
+        <v>52</v>
       </c>
       <c r="H143" s="10"/>
     </row>
@@ -10914,21 +10943,22 @@
         <v>142</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>113</v>
+        <v>208</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>114</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="H144" s="10"/>
     </row>
     <row r="145" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="9" t="n">
         <v>143</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10936,32 +10966,32 @@
         <v>144</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="B147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C147" s="18" t="n">
-        <v>0</v>
+      <c r="B147" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C147" s="18" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="9" t="n">
         <v>146</v>
       </c>
-      <c r="B148" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C148" s="18" t="s">
-        <v>119</v>
+      <c r="B148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C148" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10969,79 +10999,86 @@
         <v>147</v>
       </c>
       <c r="B149" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C149" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C149" s="18" t="s">
+      <c r="C150" s="18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="27"/>
-      <c r="B150" s="27"/>
-      <c r="C150" s="28"/>
-      <c r="D150" s="29"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="29"/>
-    </row>
     <row r="151" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="18"/>
-      <c r="B151" s="18"/>
-      <c r="C151" s="0"/>
+      <c r="A151" s="27"/>
+      <c r="B151" s="27"/>
+      <c r="C151" s="28"/>
+      <c r="D151" s="29"/>
+      <c r="E151" s="29"/>
+      <c r="F151" s="29"/>
+      <c r="G151" s="29"/>
     </row>
     <row r="152" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="18"/>
       <c r="B152" s="18"/>
-      <c r="C152" s="0"/>
+      <c r="C152" s="15"/>
     </row>
     <row r="153" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="18"/>
       <c r="B153" s="18"/>
-      <c r="C153" s="0"/>
+      <c r="C153" s="15"/>
     </row>
     <row r="154" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="18"/>
       <c r="B154" s="18"/>
-      <c r="C154" s="0"/>
+      <c r="C154" s="15"/>
     </row>
     <row r="155" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="18"/>
       <c r="B155" s="18"/>
-      <c r="C155" s="0"/>
+      <c r="C155" s="15"/>
     </row>
     <row r="156" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="18"/>
       <c r="B156" s="18"/>
-      <c r="C156" s="0"/>
+      <c r="C156" s="15"/>
     </row>
     <row r="157" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="18"/>
       <c r="B157" s="18"/>
-      <c r="C157" s="0"/>
+      <c r="C157" s="15"/>
     </row>
     <row r="158" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="18"/>
       <c r="B158" s="18"/>
-      <c r="C158" s="0"/>
+      <c r="C158" s="15"/>
     </row>
     <row r="159" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="18"/>
       <c r="B159" s="18"/>
-      <c r="C159" s="0"/>
+      <c r="C159" s="15"/>
     </row>
     <row r="160" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="18"/>
       <c r="B160" s="18"/>
-      <c r="C160" s="0"/>
+      <c r="C160" s="15"/>
     </row>
     <row r="161" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="18"/>
       <c r="B161" s="18"/>
-      <c r="C161" s="0"/>
+      <c r="C161" s="15"/>
     </row>
     <row r="162" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="18"/>
       <c r="B162" s="18"/>
+      <c r="C162" s="15"/>
     </row>
     <row r="163" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="18"/>
@@ -11151,7 +11188,10 @@
       <c r="A189" s="18"/>
       <c r="B189" s="18"/>
     </row>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="18"/>
+      <c r="B190" s="18"/>
+    </row>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -11181,82 +11221,4 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:C15"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="55.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="87.08"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="30"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="15"/>
-      <c r="C3" s="30"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="15"/>
-      <c r="C4" s="30"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="15"/>
-      <c r="C5" s="30"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="15"/>
-      <c r="C6" s="30"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15"/>
-      <c r="C7" s="30"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="15"/>
-      <c r="C8" s="30"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="15"/>
-      <c r="C9" s="30"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="15"/>
-      <c r="C10" s="30"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="15"/>
-      <c r="C11" s="30"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="15"/>
-      <c r="C12" s="30"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15"/>
-      <c r="C13" s="30"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15"/>
-      <c r="C14" s="30"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15"/>
-      <c r="C15" s="30"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>